--- a/courses_data/voc/BBA_REGISTRATION_25_28.xlsx
+++ b/courses_data/voc/BBA_REGISTRATION_25_28.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="487">
   <si>
     <t>SL NO.</t>
   </si>
@@ -35,7 +35,7 @@
     <t>STUDENT NAME</t>
   </si>
   <si>
-    <t xml:space="preserve">STUDENT NAME IN HINDI    </t>
+    <t>STUDENT NAME IN HINDI</t>
   </si>
   <si>
     <t>FATHER'S NAME</t>
@@ -47,13 +47,10 @@
     <t>COURSE</t>
   </si>
   <si>
-    <t>Batch</t>
-  </si>
-  <si>
     <t>GENDER</t>
   </si>
   <si>
-    <t>CATEGORY</t>
+    <t>CASTE</t>
   </si>
   <si>
     <t>DOB</t>
@@ -62,19 +59,22 @@
     <t>MOBILE NO</t>
   </si>
   <si>
-    <t>AADHAR NO.</t>
+    <t>Aadhaar number</t>
   </si>
   <si>
     <t>EMAIL</t>
   </si>
   <si>
-    <t>MIGRATION SUBMITTED                               (YES / NO)</t>
+    <t xml:space="preserve">MIGRATION SUBMITTED </t>
   </si>
   <si>
     <t>LAST ATTENDED UNIVERSITY</t>
   </si>
   <si>
-    <t>COLLEGE</t>
+    <t>BATCH</t>
+  </si>
+  <si>
+    <t>COLLEGE NAME</t>
   </si>
   <si>
     <t>College Code</t>
@@ -83,7 +83,7 @@
     <t>APARNA SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">अपर्णा सिंह </t>
+    <t>अपर्णा सिंह</t>
   </si>
   <si>
     <t>KRISHNA KUMAR SINGH</t>
@@ -95,15 +95,15 @@
     <t>BBA HONS.</t>
   </si>
   <si>
-    <t>2025-2028</t>
-  </si>
-  <si>
     <t>FEMALE</t>
   </si>
   <si>
     <t>GENERAL</t>
   </si>
   <si>
+    <t>244329186693</t>
+  </si>
+  <si>
     <t>aparna01singh07@gmail.com</t>
   </si>
   <si>
@@ -113,13 +113,16 @@
     <t>BSEB</t>
   </si>
   <si>
+    <t xml:space="preserve"> 2025-28</t>
+  </si>
+  <si>
     <t>purnea college ,purnia</t>
   </si>
   <si>
     <t>PRANAV MISHRA</t>
   </si>
   <si>
-    <t xml:space="preserve">प्रणव मिश्रा </t>
+    <t>प्रणव मिश्रा</t>
   </si>
   <si>
     <t>SANJAY MISHRA</t>
@@ -131,6 +134,9 @@
     <t>MALE</t>
   </si>
   <si>
+    <t>477176907233</t>
+  </si>
+  <si>
     <t>montymishra1936@gmail.com</t>
   </si>
   <si>
@@ -140,7 +146,7 @@
     <t>KAVYA KUMARI</t>
   </si>
   <si>
-    <t xml:space="preserve">काव्या कुमारी </t>
+    <t>काव्या कुमारी</t>
   </si>
   <si>
     <t>AMIT KUMARI SINGH</t>
@@ -215,7 +221,7 @@
     <t>RISHAV KARAN</t>
   </si>
   <si>
-    <t>ऋषव  करण</t>
+    <t>ऋषव करण</t>
   </si>
   <si>
     <t>AMIT ANAND</t>
@@ -230,7 +236,7 @@
     <t>RAJ ANAND</t>
   </si>
   <si>
-    <t xml:space="preserve">राज  आनंद </t>
+    <t>राज आनंद</t>
   </si>
   <si>
     <t>HARI KISHOR SINGH</t>
@@ -245,7 +251,7 @@
     <t>ADITI ANAND</t>
   </si>
   <si>
-    <t xml:space="preserve">अदिति आनंद </t>
+    <t>अदिति आनंद</t>
   </si>
   <si>
     <t>MITHILESH KUMAR JHA</t>
@@ -260,7 +266,7 @@
     <t>PRABHAT KUMAR SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">प्रभात कुमार सिंह </t>
+    <t>प्रभात कुमार सिंह</t>
   </si>
   <si>
     <t>RAKESH KUMAR SINGH</t>
@@ -278,7 +284,7 @@
     <t>PREM KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">प्रेम कुमार </t>
+    <t>प्रेम कुमार</t>
   </si>
   <si>
     <t>SURENDRA KUMAR</t>
@@ -296,7 +302,7 @@
     <t>OM KUMAR SONI</t>
   </si>
   <si>
-    <t xml:space="preserve">ओम कुमार सोनी </t>
+    <t>ओम कुमार सोनी</t>
   </si>
   <si>
     <t>KUNDAN KUMAR SAH</t>
@@ -308,7 +314,7 @@
     <t>PRIYANSHU RAJ</t>
   </si>
   <si>
-    <t xml:space="preserve">प्रियांशु राज </t>
+    <t>प्रियांशु राज</t>
   </si>
   <si>
     <t>MANOJ THAKUR</t>
@@ -323,7 +329,7 @@
     <t>SONU KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">सोनू कुमार </t>
+    <t>सोनू कुमार</t>
   </si>
   <si>
     <t>SANJEEV KUMAR</t>
@@ -338,7 +344,7 @@
     <t>AMJAD SULTANI</t>
   </si>
   <si>
-    <t xml:space="preserve">अमजद सुल्तानी </t>
+    <t>अमजद सुल्तानी</t>
   </si>
   <si>
     <t>MD SHAHUDUL HAQUE</t>
@@ -353,7 +359,7 @@
     <t>KESHAV KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">केशव कुमार </t>
+    <t>केशव कुमार</t>
   </si>
   <si>
     <t>PRATYUSH KUMR SINGH</t>
@@ -368,7 +374,7 @@
     <t>NIKHIL KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">निखिल कुमार </t>
+    <t>निखिल कुमार</t>
   </si>
   <si>
     <t>ANIL KUMAR JHA</t>
@@ -383,7 +389,7 @@
     <t>RAHUL KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">राहुल कुमार </t>
+    <t>राहुल कुमार</t>
   </si>
   <si>
     <t>SUBODH SHARMA</t>
@@ -398,7 +404,7 @@
     <t>HARSH KUMAR SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">हर्ष कुमार सिंह </t>
+    <t>हर्ष कुमार सिंह</t>
   </si>
   <si>
     <t>SUDHIR PRASAD SINGH</t>
@@ -410,7 +416,7 @@
     <t>VISHAL KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">विशाल कुमार </t>
+    <t>विशाल कुमार</t>
   </si>
   <si>
     <t>TUNTUN CHOUDHARY</t>
@@ -425,7 +431,7 @@
     <t>ASHISH KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">आशीष कुमार </t>
+    <t>आशीष कुमार</t>
   </si>
   <si>
     <t>BHUSHAN KUMAR SINGH</t>
@@ -440,7 +446,7 @@
     <t>PRITAM KUMAR SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">प्रीतम कुमार सिंह </t>
+    <t>प्रीतम कुमार सिंह</t>
   </si>
   <si>
     <t>SHANKAR KUMAR SINGH</t>
@@ -455,7 +461,7 @@
     <t>VICKY KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">विकी कुमार </t>
+    <t>विकी कुमार</t>
   </si>
   <si>
     <t>SADANAND SAH</t>
@@ -467,7 +473,7 @@
     <t>RONAK KUMAR SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">रौनक कुमार सिंह </t>
+    <t>रौनक कुमार सिंह</t>
   </si>
   <si>
     <t>RAVI KUMAR SINGH</t>
@@ -482,7 +488,7 @@
     <t>ANNU ANAND</t>
   </si>
   <si>
-    <t xml:space="preserve">अन्नू आनंद </t>
+    <t>अन्नू आनंद</t>
   </si>
   <si>
     <t>NAVIN KUMAR SINGH</t>
@@ -497,7 +503,7 @@
     <t>VIVEK SINHA</t>
   </si>
   <si>
-    <t xml:space="preserve">विवेक सिन्हा </t>
+    <t>विवेक सिन्हा</t>
   </si>
   <si>
     <t>ANIMESH KUMAR</t>
@@ -512,7 +518,7 @@
     <t>RAFAT JAHAN</t>
   </si>
   <si>
-    <t xml:space="preserve">रफत जहाँ </t>
+    <t>रफत जहाँ</t>
   </si>
   <si>
     <t>MD HASIM</t>
@@ -530,7 +536,7 @@
     <t>RAJ KAMAL THAKUR</t>
   </si>
   <si>
-    <t xml:space="preserve">राज कमल ठाकुर </t>
+    <t>राज कमल ठाकुर</t>
   </si>
   <si>
     <t>PANKAJ KUMAR THAKUR</t>
@@ -545,7 +551,7 @@
     <t>AMAN KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">अमन कुमार </t>
+    <t>अमन कुमार</t>
   </si>
   <si>
     <t>SANJAY MANDAL</t>
@@ -560,7 +566,7 @@
     <t>PETER DAS</t>
   </si>
   <si>
-    <t xml:space="preserve">पीटर दास </t>
+    <t>पीटर दास</t>
   </si>
   <si>
     <t>JHULAN KUMAR DAS</t>
@@ -578,7 +584,7 @@
     <t>RIHAN KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">रिहान कुमार </t>
+    <t>रिहान कुमार</t>
   </si>
   <si>
     <t>SHARWAN KUMAR DAS</t>
@@ -593,7 +599,7 @@
     <t>BHANU KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">भानु कुमार </t>
+    <t>भानु कुमार</t>
   </si>
   <si>
     <t>NAVAL KISHOR YADAV</t>
@@ -608,7 +614,7 @@
     <t>HIMANSHU KUMAR SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">हिमांशु कुमार सिंह </t>
+    <t>हिमांशु कुमार सिंह</t>
   </si>
   <si>
     <t>SANOJ KUMAR SINGH</t>
@@ -623,7 +629,7 @@
     <t>RAJ HANS</t>
   </si>
   <si>
-    <t xml:space="preserve">राज हंस </t>
+    <t>राज हंस</t>
   </si>
   <si>
     <t>BIJENDRA JHA</t>
@@ -638,7 +644,7 @@
     <t>AJEET KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">अजीत कुमार </t>
+    <t>अजीत कुमार</t>
   </si>
   <si>
     <t>VIJAY KUMAR SINGH</t>
@@ -653,7 +659,7 @@
     <t>VISHWAJEET THAKUR</t>
   </si>
   <si>
-    <t xml:space="preserve">विश्वजीत ठाकुर </t>
+    <t>विश्वजीत ठाकुर</t>
   </si>
   <si>
     <t>SANOJA THAKUR</t>
@@ -665,7 +671,7 @@
     <t>PRINCE KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">प्रिंस कुमार </t>
+    <t>प्रिंस कुमार</t>
   </si>
   <si>
     <t>KISHOR KUMAR YADAV</t>
@@ -680,7 +686,7 @@
     <t>SUNNY KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">सनी कुमार </t>
+    <t>सनी कुमार</t>
   </si>
   <si>
     <t>SANTOSH KUMAR SINGH</t>
@@ -695,7 +701,7 @@
     <t>BABUL KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">बाबुल कुमार </t>
+    <t>बाबुल कुमार</t>
   </si>
   <si>
     <t>RANJAY YADAV</t>
@@ -752,7 +758,7 @@
     <t>NANCY SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">नैंसी सिंह </t>
+    <t>नैंसी सिंह</t>
   </si>
   <si>
     <t>AMIT KUMAR SINGH</t>
@@ -767,7 +773,7 @@
     <t>BADAL SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">बादल सिंह </t>
+    <t>बादल सिंह</t>
   </si>
   <si>
     <t>AMOD SINGH</t>
@@ -782,7 +788,7 @@
     <t>ANKIT KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">अंकित कुमार </t>
+    <t>अंकित कुमार</t>
   </si>
   <si>
     <t>BIRENDRA KUMAR</t>
@@ -797,7 +803,7 @@
     <t>RISHABH RAJ</t>
   </si>
   <si>
-    <t xml:space="preserve">ऋषभ राज </t>
+    <t>ऋषभ राज</t>
   </si>
   <si>
     <t>LT ANJANI KUMAR SHARAN</t>
@@ -812,7 +818,7 @@
     <t>ARYAN KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">आर्यन कुमार </t>
+    <t>आर्यन कुमार</t>
   </si>
   <si>
     <t>ANIL KUMAR CHOUDHARY</t>
@@ -827,7 +833,7 @@
     <t>AMAN RAJ</t>
   </si>
   <si>
-    <t xml:space="preserve">अमन राज </t>
+    <t>अमन राज</t>
   </si>
   <si>
     <t>RUPESH KUMAR JHA</t>
@@ -842,7 +848,7 @@
     <t>ADITYA KUMAR VISHWAS</t>
   </si>
   <si>
-    <t xml:space="preserve">आदित्य कुमार विश्वास </t>
+    <t>आदित्य कुमार विश्वास</t>
   </si>
   <si>
     <t>ROHIT KUMAR VISHWAS</t>
@@ -857,7 +863,7 @@
     <t>BHAWESH KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">भवेश कुमार </t>
+    <t>भवेश कुमार</t>
   </si>
   <si>
     <t>RAJESH KUMAR MEHTA</t>
@@ -872,7 +878,7 @@
     <t>KRISHU RAJ</t>
   </si>
   <si>
-    <t xml:space="preserve">कृशु राज </t>
+    <t>कृशु राज</t>
   </si>
   <si>
     <t>RANJEET KUMAR</t>
@@ -887,7 +893,7 @@
     <t>ARYA RAJ SINGH</t>
   </si>
   <si>
-    <t xml:space="preserve">आर्या राज सिंह </t>
+    <t>आर्या राज सिंह</t>
   </si>
   <si>
     <t>NIL MANI SINGH</t>
@@ -902,7 +908,7 @@
     <t>RIYA SHARMA</t>
   </si>
   <si>
-    <t xml:space="preserve">रिया शर्मा </t>
+    <t>रिया शर्मा</t>
   </si>
   <si>
     <t>SANJAY KUMAR SHARMA</t>
@@ -917,7 +923,7 @@
     <t>ASHUTOSH KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">आशुतोष कुमार </t>
+    <t>आशुतोष कुमार</t>
   </si>
   <si>
     <t>INDRABHUSHAN SINGH</t>
@@ -929,7 +935,7 @@
     <t>MOHIT KUMAR</t>
   </si>
   <si>
-    <t xml:space="preserve">मोहित कुमार </t>
+    <t>मोहित कुमार</t>
   </si>
   <si>
     <t>MANOJ KUMAR SINHA</t>
@@ -950,7 +956,7 @@
     <t>UTSAV NATH TIWARI</t>
   </si>
   <si>
-    <t xml:space="preserve">उत्सव नाथ तिवारी </t>
+    <t>उत्सव नाथ तिवारी</t>
   </si>
   <si>
     <t>DHARMENDRA NATH TIWARI</t>
@@ -962,7 +968,7 @@
     <t>utsavtiwari045@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">ADITYA KUMAR  </t>
+    <t>ADITYA KUMAR</t>
   </si>
   <si>
     <t>आदित्य कुमार</t>
@@ -998,7 +1004,7 @@
     <t>komalkumari54343489000@gmail.com</t>
   </si>
   <si>
-    <t>B. S. E. B.  PATNA</t>
+    <t>B. S. E. B. PATNA</t>
   </si>
   <si>
     <t>purnea mahila college, purnia</t>
@@ -1025,10 +1031,10 @@
     <t>P.M.C.</t>
   </si>
   <si>
-    <t xml:space="preserve">VAISHNAVI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">वैष्णवी </t>
+    <t>VAISHNAVI</t>
+  </si>
+  <si>
+    <t>वैष्णवी</t>
   </si>
   <si>
     <t>PRABHAT KUMAR DUTTA</t>
@@ -1085,7 +1091,7 @@
     <t>साक्षी झा</t>
   </si>
   <si>
-    <t xml:space="preserve">KAMLESH KUMAR JHA </t>
+    <t>KAMLESH KUMAR JHA</t>
   </si>
   <si>
     <t>8996 4102 8679</t>
@@ -1112,13 +1118,13 @@
     <t>khushi22sinha@gmail.com</t>
   </si>
   <si>
-    <t xml:space="preserve">AKANKSHI SAH </t>
+    <t>AKANKSHI SAH</t>
   </si>
   <si>
     <t>अंकाक्षी साह</t>
   </si>
   <si>
-    <t xml:space="preserve">RAJEEV KUMAR SAH </t>
+    <t>RAJEEV KUMAR SAH</t>
   </si>
   <si>
     <t>PRAMILA DEVI</t>
@@ -1127,16 +1133,16 @@
     <t>3383 0082 3375</t>
   </si>
   <si>
-    <t xml:space="preserve">SHISHTI </t>
-  </si>
-  <si>
-    <t xml:space="preserve">शिष्टी </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHASHI KANT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PUNAM KUMARI SHRIVASTAVA </t>
+    <t>SHISHTI</t>
+  </si>
+  <si>
+    <t>शिष्टी</t>
+  </si>
+  <si>
+    <t>SHASHI KANT</t>
+  </si>
+  <si>
+    <t>PUNAM KUMARI SHRIVASTAVA</t>
   </si>
   <si>
     <t>5336 5587 4193</t>
@@ -1172,7 +1178,7 @@
     <t>रजिया सुल्ताना</t>
   </si>
   <si>
-    <t xml:space="preserve">MD. NURUL </t>
+    <t>MD. NURUL</t>
   </si>
   <si>
     <t>KHURSHIDA KHATOON</t>
@@ -1202,7 +1208,7 @@
     <t>शम्भवी कुमारी</t>
   </si>
   <si>
-    <t xml:space="preserve">SANTOSH KUMAR CHOUDHARY </t>
+    <t>SANTOSH KUMAR CHOUDHARY</t>
   </si>
   <si>
     <t>SANGITA DEVI</t>
@@ -1214,7 +1220,7 @@
     <t>DAYANAND SAH</t>
   </si>
   <si>
-    <t xml:space="preserve">2823 4232 8461 </t>
+    <t>2823 4232 8461</t>
   </si>
   <si>
     <t>priyasah335092@gmail.com</t>
@@ -1250,7 +1256,7 @@
     <t>MD HASIB ANSARI</t>
   </si>
   <si>
-    <t xml:space="preserve">RUHI BEGUM </t>
+    <t>RUHI BEGUM</t>
   </si>
   <si>
     <t>4331 1765 2267</t>
@@ -1439,7 +1445,7 @@
     <t>MD HAMID IQUBAL</t>
   </si>
   <si>
-    <t xml:space="preserve"> मो० हामिद इकबाल</t>
+    <t>मो० हामिद इकबाल</t>
   </si>
   <si>
     <t>MD MUSHTAQUE AHMAD</t>
@@ -1463,7 +1469,7 @@
     <t>YOGITA THAKUR</t>
   </si>
   <si>
-    <t xml:space="preserve">योगिता ठाकुर </t>
+    <t>योगिता ठाकुर</t>
   </si>
   <si>
     <t>RAJESH THAKUR</t>
@@ -2102,24 +2108,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2596,127 +2594,127 @@
   <dimension ref="A1:Q87"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="36" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7" style="1" customWidth="1"/>
-    <col min="2" max="3" width="21.4259259259259" style="1" customWidth="1"/>
-    <col min="4" max="4" width="29.287037037037" style="1" customWidth="1"/>
-    <col min="5" max="5" width="29.4259259259259" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.1666666666667" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.3425925925926" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.0462962962963" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7037037037037" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.3240740740741" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.7962962962963" style="1" customWidth="1"/>
-    <col min="12" max="12" width="18.5740740740741" style="1" customWidth="1"/>
-    <col min="13" max="13" width="31.712962962963" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17.0648148148148" style="1" customWidth="1"/>
-    <col min="15" max="15" width="28.1759259259259" style="1" customWidth="1"/>
-    <col min="16" max="16" width="24.3333333333333" style="1" customWidth="1"/>
-    <col min="17" max="17" width="19.6666666666667" style="1" customWidth="1"/>
-    <col min="18" max="27" width="8.71296296296296" style="1" customWidth="1"/>
-    <col min="28" max="16384" width="8.88888888888889" style="1"/>
+    <col min="1" max="1" width="7" style="2" customWidth="1"/>
+    <col min="2" max="3" width="21.4259259259259" style="2" customWidth="1"/>
+    <col min="4" max="4" width="29.287037037037" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.4259259259259" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.1666666666667" style="2" customWidth="1"/>
+    <col min="7" max="7" width="17.3425925925926" style="2" customWidth="1"/>
+    <col min="8" max="8" width="15.0462962962963" style="2" customWidth="1"/>
+    <col min="9" max="9" width="18.7037037037037" style="2" customWidth="1"/>
+    <col min="10" max="10" width="31.4351851851852" style="2" customWidth="1"/>
+    <col min="11" max="11" width="16.7962962962963" style="2" customWidth="1"/>
+    <col min="12" max="12" width="40.3703703703704" style="2" customWidth="1"/>
+    <col min="13" max="13" width="31.712962962963" style="2" customWidth="1"/>
+    <col min="14" max="14" width="41.3240740740741" style="2" customWidth="1"/>
+    <col min="15" max="15" width="28.1759259259259" style="2" customWidth="1"/>
+    <col min="16" max="16" width="28.712962962963" style="2" customWidth="1"/>
+    <col min="17" max="17" width="22.6203703703704" style="2" customWidth="1"/>
+    <col min="18" max="26" width="8.71296296296296" style="2" customWidth="1"/>
+    <col min="27" max="16384" width="8.88888888888889" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:17">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" ht="56.25" customHeight="1" spans="1:17">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:17">
-      <c r="A2" s="3">
+    <row r="2" s="2" customFormat="1" customHeight="1" spans="1:17">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="4">
+        <v>39142</v>
+      </c>
+      <c r="J2" s="4">
+        <v>9241553411</v>
+      </c>
+      <c r="K2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="3">
-        <v>39142</v>
-      </c>
-      <c r="K2" s="3">
-        <v>9241553411</v>
-      </c>
-      <c r="L2" s="3">
-        <v>244329186693</v>
-      </c>
-      <c r="M2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O2" s="4" t="s">
+      <c r="M2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>28</v>
+      <c r="O2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="Q2" s="5">
         <v>12</v>
@@ -2726,50 +2724,50 @@
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>24</v>
+      <c r="G3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="5">
+        <v>38718</v>
       </c>
       <c r="J3" s="5">
-        <v>38718</v>
-      </c>
-      <c r="K3" s="5">
         <v>7562952191</v>
       </c>
-      <c r="L3" s="5">
-        <v>477176907233</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="K3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>35</v>
+      <c r="O3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q3" s="5">
         <v>12</v>
@@ -2779,50 +2777,50 @@
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5">
+        <v>38702</v>
+      </c>
+      <c r="J4" s="5">
+        <v>9304023707</v>
+      </c>
+      <c r="K4" s="5">
+        <v>494115654236</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="5">
-        <v>38702</v>
-      </c>
-      <c r="K4" s="5">
-        <v>9304023707</v>
-      </c>
-      <c r="L4" s="5">
-        <v>494115654236</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="Q4" s="5">
         <v>12</v>
@@ -2832,50 +2830,50 @@
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>24</v>
+      <c r="G5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="5">
+        <v>39083</v>
       </c>
       <c r="J5" s="5">
-        <v>39083</v>
+        <v>9523768961</v>
       </c>
       <c r="K5" s="5">
-        <v>9523768961</v>
-      </c>
-      <c r="L5" s="5">
         <v>436353627288</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O5" s="2" t="s">
+      <c r="L5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P5" s="2" t="s">
-        <v>35</v>
+      <c r="O5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q5" s="5">
         <v>12</v>
@@ -2885,50 +2883,50 @@
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>24</v>
+      <c r="G6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" s="5">
+        <v>39128</v>
       </c>
       <c r="J6" s="5">
-        <v>39128</v>
+        <v>8210827625</v>
       </c>
       <c r="K6" s="5">
-        <v>8210827625</v>
-      </c>
-      <c r="L6" s="5">
         <v>938859763401</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O6" s="2" t="s">
+      <c r="L6" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>35</v>
+      <c r="O6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q6" s="5">
         <v>12</v>
@@ -2938,50 +2936,50 @@
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2" t="s">
+      <c r="B7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>24</v>
+      <c r="G7" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="5">
+        <v>39083</v>
       </c>
       <c r="J7" s="5">
-        <v>39083</v>
+        <v>6205870747</v>
       </c>
       <c r="K7" s="5">
-        <v>6205870747</v>
-      </c>
-      <c r="L7" s="5">
         <v>799063069895</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="L7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>35</v>
+      <c r="O7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q7" s="5">
         <v>12</v>
@@ -2991,50 +2989,50 @@
       <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="D8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>59</v>
+      <c r="G8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="5">
+        <v>39441</v>
       </c>
       <c r="J8" s="5">
-        <v>39441</v>
+        <v>7492955051</v>
       </c>
       <c r="K8" s="5">
-        <v>7492955051</v>
-      </c>
-      <c r="L8" s="5">
         <v>867090074999</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O8" s="2" t="s">
+      <c r="L8" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>35</v>
+      <c r="O8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q8" s="5">
         <v>12</v>
@@ -3044,50 +3042,50 @@
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="D9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>24</v>
+      <c r="G9" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" s="5">
+        <v>39267</v>
       </c>
       <c r="J9" s="5">
-        <v>39267</v>
+        <v>9135003875</v>
       </c>
       <c r="K9" s="5">
-        <v>9135003875</v>
-      </c>
-      <c r="L9" s="5">
         <v>262701879757</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O9" s="2" t="s">
+      <c r="L9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>35</v>
+      <c r="O9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q9" s="5">
         <v>12</v>
@@ -3097,50 +3095,50 @@
       <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="D10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>24</v>
+      <c r="G10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" s="5">
+        <v>39086</v>
       </c>
       <c r="J10" s="5">
-        <v>39086</v>
+        <v>7644843560</v>
       </c>
       <c r="K10" s="5">
-        <v>7644843560</v>
-      </c>
-      <c r="L10" s="5">
         <v>626620985360</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O10" s="2" t="s">
+      <c r="L10" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>35</v>
+      <c r="O10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q10" s="5">
         <v>12</v>
@@ -3150,50 +3148,50 @@
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="D11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="H11" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I11" s="2" t="s">
-        <v>24</v>
+      <c r="I11" s="5">
+        <v>39447</v>
       </c>
       <c r="J11" s="5">
-        <v>39447</v>
+        <v>9661922698</v>
       </c>
       <c r="K11" s="5">
-        <v>9661922698</v>
-      </c>
-      <c r="L11" s="5">
         <v>724383297941</v>
       </c>
-      <c r="M11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O11" s="2" t="s">
+      <c r="L11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>35</v>
+      <c r="O11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q11" s="5">
         <v>12</v>
@@ -3203,50 +3201,50 @@
       <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="B12" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="C12" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="D12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>24</v>
+      <c r="G12" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="5">
+        <v>36380</v>
       </c>
       <c r="J12" s="5">
-        <v>36380</v>
+        <v>6287745156</v>
       </c>
       <c r="K12" s="5">
-        <v>6287745156</v>
-      </c>
-      <c r="L12" s="5">
         <v>201516973219</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O12" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>35</v>
+      <c r="L12" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q12" s="5">
         <v>12</v>
@@ -3256,50 +3254,50 @@
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="B13" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="D13" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>86</v>
+      <c r="G13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" s="5">
+        <v>39083</v>
       </c>
       <c r="J13" s="5">
-        <v>39083</v>
+        <v>7484881090</v>
       </c>
       <c r="K13" s="5">
-        <v>7484881090</v>
-      </c>
-      <c r="L13" s="5">
         <v>484133372544</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="2" t="s">
+      <c r="L13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>35</v>
+      <c r="O13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q13" s="5">
         <v>12</v>
@@ -3309,50 +3307,50 @@
       <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>86</v>
+      <c r="I14" s="5">
+        <v>38843</v>
       </c>
       <c r="J14" s="5">
-        <v>38843</v>
+        <v>8271304979</v>
       </c>
       <c r="K14" s="5">
-        <v>8271304979</v>
-      </c>
-      <c r="L14" s="5">
         <v>870816282803</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O14" s="2" t="s">
+      <c r="L14" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>35</v>
+      <c r="O14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q14" s="5">
         <v>12</v>
@@ -3362,50 +3360,50 @@
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="B15" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="C15" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="D15" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>24</v>
+      <c r="G15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I15" s="5">
+        <v>39375</v>
       </c>
       <c r="J15" s="5">
-        <v>39375</v>
+        <v>9661783704</v>
       </c>
       <c r="K15" s="5">
-        <v>9661783704</v>
-      </c>
-      <c r="L15" s="5">
         <v>900588214895</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="2" t="s">
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>35</v>
+      <c r="O15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q15" s="5">
         <v>12</v>
@@ -3415,50 +3413,50 @@
       <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="B16" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="C16" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="D16" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>59</v>
+      <c r="G16" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="5">
+        <v>38750</v>
       </c>
       <c r="J16" s="5">
-        <v>38750</v>
+        <v>6206323488</v>
       </c>
       <c r="K16" s="5">
-        <v>6206323488</v>
-      </c>
-      <c r="L16" s="5">
         <v>928751303587</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P16" s="2" t="s">
-        <v>35</v>
+      <c r="L16" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q16" s="5">
         <v>12</v>
@@ -3468,50 +3466,50 @@
       <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D17" s="2" t="s">
+      <c r="B17" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>24</v>
+      <c r="G17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I17" s="5">
+        <v>38920</v>
       </c>
       <c r="J17" s="5">
-        <v>38920</v>
+        <v>6200769729</v>
       </c>
       <c r="K17" s="5">
-        <v>6200769729</v>
-      </c>
-      <c r="L17" s="5">
         <v>798246280906</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O17" s="2" t="s">
+      <c r="L17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>35</v>
+      <c r="O17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q17" s="5">
         <v>12</v>
@@ -3521,50 +3519,50 @@
       <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="B18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="C18" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="D18" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>24</v>
+      <c r="G18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="5">
+        <v>39409</v>
       </c>
       <c r="J18" s="5">
-        <v>39409</v>
+        <v>9709736837</v>
       </c>
       <c r="K18" s="5">
-        <v>9709736837</v>
-      </c>
-      <c r="L18" s="5">
         <v>572740617423</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="2" t="s">
+      <c r="L18" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>35</v>
+      <c r="O18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q18" s="5">
         <v>12</v>
@@ -3574,50 +3572,50 @@
       <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="B19" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="D19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>24</v>
+      <c r="G19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="5">
+        <v>38718</v>
       </c>
       <c r="J19" s="5">
-        <v>38718</v>
+        <v>9931529698</v>
       </c>
       <c r="K19" s="5">
-        <v>9931529698</v>
-      </c>
-      <c r="L19" s="5">
         <v>486228222169</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O19" s="2" t="s">
+      <c r="L19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>35</v>
+      <c r="O19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q19" s="5">
         <v>12</v>
@@ -3627,50 +3625,50 @@
       <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="B20" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="D20" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>59</v>
+      <c r="G20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="5">
+        <v>38858</v>
       </c>
       <c r="J20" s="5">
-        <v>38858</v>
+        <v>7070308449</v>
       </c>
       <c r="K20" s="5">
-        <v>7070308449</v>
-      </c>
-      <c r="L20" s="5">
         <v>350527657469</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O20" s="2" t="s">
+      <c r="L20" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>35</v>
+      <c r="O20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q20" s="5">
         <v>12</v>
@@ -3680,50 +3678,50 @@
       <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="B21" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F21" s="2" t="s">
+      <c r="C21" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>24</v>
+      <c r="G21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I21" s="5">
+        <v>39629</v>
       </c>
       <c r="J21" s="5">
-        <v>39629</v>
+        <v>9798494536</v>
       </c>
       <c r="K21" s="5">
-        <v>9798494536</v>
-      </c>
-      <c r="L21" s="5">
         <v>353091874453</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O21" s="2" t="s">
+      <c r="L21" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>35</v>
+      <c r="O21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q21" s="5">
         <v>12</v>
@@ -3733,50 +3731,50 @@
       <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" s="2" t="s">
+      <c r="B22" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="C22" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="D22" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>86</v>
+      <c r="G22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I22" s="5">
+        <v>39342</v>
       </c>
       <c r="J22" s="5">
-        <v>39342</v>
+        <v>8797085517</v>
       </c>
       <c r="K22" s="5">
-        <v>8797085517</v>
-      </c>
-      <c r="L22" s="5">
         <v>496422455364</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O22" s="2" t="s">
+      <c r="L22" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P22" s="2" t="s">
-        <v>35</v>
+      <c r="O22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q22" s="5">
         <v>12</v>
@@ -3786,50 +3784,50 @@
       <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="B23" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="C23" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="D23" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>24</v>
+      <c r="G23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I23" s="5">
+        <v>39451</v>
       </c>
       <c r="J23" s="5">
-        <v>39451</v>
+        <v>9234189060</v>
       </c>
       <c r="K23" s="5">
-        <v>9234189060</v>
-      </c>
-      <c r="L23" s="5">
         <v>310093163015</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O23" s="2" t="s">
+      <c r="L23" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P23" s="2" t="s">
-        <v>35</v>
+      <c r="O23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q23" s="5">
         <v>12</v>
@@ -3839,50 +3837,50 @@
       <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="B24" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="C24" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="D24" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>24</v>
+      <c r="G24" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I24" s="5">
+        <v>39141</v>
       </c>
       <c r="J24" s="5">
-        <v>39141</v>
+        <v>6207149615</v>
       </c>
       <c r="K24" s="5">
-        <v>6207149615</v>
-      </c>
-      <c r="L24" s="5">
         <v>432472642620</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O24" s="2" t="s">
+      <c r="L24" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M24" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>35</v>
+      <c r="O24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q24" s="5">
         <v>12</v>
@@ -3892,50 +3890,50 @@
       <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="F25" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>59</v>
+      <c r="G25" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25" s="5">
+        <v>39577</v>
       </c>
       <c r="J25" s="5">
-        <v>39577</v>
+        <v>7667694462</v>
       </c>
       <c r="K25" s="5">
-        <v>7667694462</v>
-      </c>
-      <c r="L25" s="5">
         <v>679076158188</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O25" s="2" t="s">
+      <c r="L25" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>35</v>
+      <c r="O25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q25" s="5">
         <v>12</v>
@@ -3945,50 +3943,50 @@
       <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="D26" s="2" t="s">
+      <c r="B26" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="C26" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="D26" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>24</v>
+      <c r="G26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="5">
+        <v>39266</v>
       </c>
       <c r="J26" s="5">
-        <v>39266</v>
+        <v>9123285411</v>
       </c>
       <c r="K26" s="5">
-        <v>9123285411</v>
-      </c>
-      <c r="L26" s="5">
         <v>718888788747</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="N26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" s="2" t="s">
+      <c r="L26" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N26" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>35</v>
+      <c r="O26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q26" s="5">
         <v>12</v>
@@ -3998,50 +3996,50 @@
       <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D27" s="2" t="s">
+      <c r="B27" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="C27" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="D27" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="H27" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>24</v>
+      <c r="I27" s="5">
+        <v>38976</v>
       </c>
       <c r="J27" s="5">
-        <v>38976</v>
+        <v>8298301950</v>
       </c>
       <c r="K27" s="5">
-        <v>8298301950</v>
-      </c>
-      <c r="L27" s="5">
         <v>887731641958</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="N27" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O27" s="2" t="s">
+      <c r="L27" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="M27" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>35</v>
+      <c r="O27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q27" s="5">
         <v>12</v>
@@ -4051,50 +4049,50 @@
       <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="B28" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="C28" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="D28" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>24</v>
+      <c r="G28" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="5">
+        <v>39696</v>
       </c>
       <c r="J28" s="5">
-        <v>39696</v>
+        <v>7808038170</v>
       </c>
       <c r="K28" s="5">
-        <v>7808038170</v>
-      </c>
-      <c r="L28" s="5">
         <v>963868749861</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O28" s="2" t="s">
+      <c r="L28" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N28" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>35</v>
+      <c r="O28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q28" s="5">
         <v>12</v>
@@ -4104,50 +4102,50 @@
       <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="B29" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="C29" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="D29" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>86</v>
+      <c r="H29" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I29" s="5">
+        <v>39157</v>
       </c>
       <c r="J29" s="5">
-        <v>39157</v>
+        <v>9193398066</v>
       </c>
       <c r="K29" s="5">
-        <v>9193398066</v>
-      </c>
-      <c r="L29" s="5">
         <v>990331303373</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>35</v>
+      <c r="L29" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="M29" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N29" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q29" s="5">
         <v>12</v>
@@ -4157,48 +4155,48 @@
       <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B30" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="C30" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="D30" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>59</v>
+      <c r="G30" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="5">
+        <v>38381</v>
       </c>
       <c r="J30" s="5">
-        <v>38381</v>
-      </c>
-      <c r="K30" s="5">
         <v>7061999873</v>
       </c>
-      <c r="L30" s="5"/>
-      <c r="M30" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O30" s="2" t="s">
+      <c r="K30" s="5"/>
+      <c r="L30" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>35</v>
+      <c r="O30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q30" s="5">
         <v>12</v>
@@ -4208,50 +4206,50 @@
       <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="B31" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="C31" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="D31" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>59</v>
+      <c r="G31" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="5">
+        <v>38353</v>
       </c>
       <c r="J31" s="5">
-        <v>38353</v>
+        <v>7739424414</v>
       </c>
       <c r="K31" s="5">
-        <v>7739424414</v>
-      </c>
-      <c r="L31" s="5">
         <v>486409871624</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="N31" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O31" s="2" t="s">
+      <c r="L31" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N31" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P31" s="2" t="s">
-        <v>35</v>
+      <c r="O31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q31" s="5">
         <v>12</v>
@@ -4261,48 +4259,48 @@
       <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="B32" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="C32" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="D32" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>180</v>
+      <c r="G32" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I32" s="5">
+        <v>39365</v>
       </c>
       <c r="J32" s="5">
-        <v>39365</v>
-      </c>
-      <c r="K32" s="5">
         <v>8076465071</v>
       </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="N32" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>35</v>
+      <c r="K32" s="5"/>
+      <c r="L32" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q32" s="5">
         <v>12</v>
@@ -4312,50 +4310,50 @@
       <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>180</v>
+      <c r="I33" s="5">
+        <v>39300</v>
       </c>
       <c r="J33" s="5">
-        <v>39300</v>
+        <v>8235312842</v>
       </c>
       <c r="K33" s="5">
-        <v>8235312842</v>
-      </c>
-      <c r="L33" s="5">
         <v>598486693624</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="N33" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O33" s="2" t="s">
+      <c r="L33" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>35</v>
+      <c r="O33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q33" s="5">
         <v>12</v>
@@ -4365,50 +4363,50 @@
       <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D34" s="2" t="s">
+      <c r="B34" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="C34" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="D34" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>86</v>
+      <c r="G34" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I34" s="5">
+        <v>39249</v>
       </c>
       <c r="J34" s="5">
-        <v>39249</v>
+        <v>7632973276</v>
       </c>
       <c r="K34" s="5">
-        <v>7632973276</v>
-      </c>
-      <c r="L34" s="5">
         <v>811760650859</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="N34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O34" s="2" t="s">
+      <c r="L34" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N34" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>35</v>
+      <c r="O34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q34" s="5">
         <v>12</v>
@@ -4418,50 +4416,50 @@
       <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D35" s="2" t="s">
+      <c r="B35" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="C35" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F35" s="2" t="s">
+      <c r="D35" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G35" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>24</v>
+      <c r="G35" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I35" s="5">
+        <v>39145</v>
       </c>
       <c r="J35" s="5">
-        <v>39145</v>
+        <v>9508534518</v>
       </c>
       <c r="K35" s="5">
-        <v>9508534518</v>
-      </c>
-      <c r="L35" s="5">
         <v>917018035841</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O35" s="2" t="s">
+      <c r="L35" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>35</v>
+      <c r="O35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q35" s="5">
         <v>12</v>
@@ -4471,48 +4469,48 @@
       <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="B36" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="C36" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="D36" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>24</v>
+      <c r="G36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I36" s="5">
+        <v>38279</v>
       </c>
       <c r="J36" s="5">
-        <v>38279</v>
-      </c>
-      <c r="K36" s="5">
         <v>7319615757</v>
       </c>
-      <c r="L36" s="5"/>
-      <c r="M36" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O36" s="2" t="s">
+      <c r="K36" s="5"/>
+      <c r="L36" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N36" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>35</v>
+      <c r="O36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q36" s="5">
         <v>12</v>
@@ -4522,50 +4520,50 @@
       <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="B37" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="C37" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F37" s="2" t="s">
+      <c r="D37" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>24</v>
+      <c r="G37" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="5">
+        <v>39755</v>
       </c>
       <c r="J37" s="5">
-        <v>39755</v>
+        <v>6203784631</v>
       </c>
       <c r="K37" s="5">
-        <v>6203784631</v>
-      </c>
-      <c r="L37" s="5">
         <v>270568562230</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O37" s="2" t="s">
+      <c r="L37" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P37" s="2" t="s">
-        <v>35</v>
+      <c r="O37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q37" s="5">
         <v>12</v>
@@ -4575,50 +4573,50 @@
       <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D38" s="2" t="s">
+      <c r="B38" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="C38" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>24</v>
+      <c r="G38" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I38" s="5">
+        <v>39054</v>
       </c>
       <c r="J38" s="5">
-        <v>39054</v>
+        <v>9973427323</v>
       </c>
       <c r="K38" s="5">
-        <v>9973427323</v>
-      </c>
-      <c r="L38" s="5">
         <v>238566876181</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O38" s="2" t="s">
+      <c r="L38" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>35</v>
+      <c r="O38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q38" s="5">
         <v>12</v>
@@ -4628,48 +4626,48 @@
       <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D39" s="2" t="s">
+      <c r="B39" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="C39" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="D39" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G39" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>86</v>
+      <c r="G39" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="5">
+        <v>38990</v>
       </c>
       <c r="J39" s="5">
-        <v>38990</v>
-      </c>
-      <c r="K39" s="5">
         <v>8709317228</v>
       </c>
-      <c r="L39" s="5"/>
-      <c r="M39" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="N39" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P39" s="2" t="s">
-        <v>35</v>
+      <c r="K39" s="5"/>
+      <c r="L39" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N39" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q39" s="5">
         <v>12</v>
@@ -4679,50 +4677,50 @@
       <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="D40" s="2" t="s">
+      <c r="B40" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="C40" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="D40" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>24</v>
+      <c r="G40" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I40" s="5">
+        <v>38505</v>
       </c>
       <c r="J40" s="5">
-        <v>38505</v>
+        <v>9279557113</v>
       </c>
       <c r="K40" s="5">
-        <v>9279557113</v>
-      </c>
-      <c r="L40" s="5">
         <v>338248853482</v>
       </c>
-      <c r="M40" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O40" s="2" t="s">
+      <c r="L40" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N40" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P40" s="2" t="s">
-        <v>35</v>
+      <c r="O40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q40" s="5">
         <v>12</v>
@@ -4732,50 +4730,50 @@
       <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="B41" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="C41" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="D41" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G41" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>86</v>
+      <c r="G41" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I41" s="5">
+        <v>38415</v>
       </c>
       <c r="J41" s="5">
-        <v>38415</v>
+        <v>9798536319</v>
       </c>
       <c r="K41" s="5">
-        <v>9798536319</v>
-      </c>
-      <c r="L41" s="5">
         <v>379241067429</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="N41" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O41" s="2" t="s">
+      <c r="L41" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N41" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>35</v>
+      <c r="O41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q41" s="5">
         <v>12</v>
@@ -4785,50 +4783,50 @@
       <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="B42" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>180</v>
+      <c r="G42" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I42" s="5">
+        <v>39265</v>
       </c>
       <c r="J42" s="5">
-        <v>39265</v>
+        <v>7250255450</v>
       </c>
       <c r="K42" s="5">
-        <v>7250255450</v>
-      </c>
-      <c r="L42" s="5">
         <v>354502140422</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O42" s="2" t="s">
+      <c r="L42" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P42" s="2" t="s">
-        <v>35</v>
+      <c r="O42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q42" s="5">
         <v>12</v>
@@ -4838,50 +4836,50 @@
       <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="B43" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="C43" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="D43" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>86</v>
+      <c r="G43" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I43" s="5">
+        <v>38353</v>
       </c>
       <c r="J43" s="5">
-        <v>38353</v>
+        <v>9934328012</v>
       </c>
       <c r="K43" s="5">
-        <v>9934328012</v>
-      </c>
-      <c r="L43" s="5">
         <v>954941892878</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O43" s="2" t="s">
+      <c r="L43" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N43" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P43" s="2" t="s">
-        <v>35</v>
+      <c r="O43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q43" s="5">
         <v>12</v>
@@ -4891,50 +4889,50 @@
       <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F44" s="2" t="s">
+      <c r="B44" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G44" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>86</v>
+      <c r="G44" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I44" s="5">
+        <v>38898</v>
       </c>
       <c r="J44" s="5">
-        <v>38898</v>
+        <v>9801637173</v>
       </c>
       <c r="K44" s="5">
-        <v>9801637173</v>
-      </c>
-      <c r="L44" s="5">
         <v>946612918405</v>
       </c>
-      <c r="M44" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O44" s="2" t="s">
+      <c r="L44" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N44" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P44" s="2" t="s">
-        <v>35</v>
+      <c r="O44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q44" s="5">
         <v>12</v>
@@ -4944,50 +4942,50 @@
       <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="B45" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>86</v>
+      <c r="G45" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I45" s="5">
+        <v>39474</v>
       </c>
       <c r="J45" s="5">
-        <v>39474</v>
+        <v>6205311654</v>
       </c>
       <c r="K45" s="5">
-        <v>6205311654</v>
-      </c>
-      <c r="L45" s="5">
         <v>834000218651</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="N45" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>35</v>
+      <c r="L45" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q45" s="5">
         <v>12</v>
@@ -4997,50 +4995,50 @@
       <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="B46" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="C46" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="D46" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F46" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G46" s="4" t="s">
+      <c r="G46" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H46" s="2" t="s">
+      <c r="H46" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>24</v>
+      <c r="I46" s="5">
+        <v>38957</v>
       </c>
       <c r="J46" s="5">
-        <v>38957</v>
+        <v>9102126441</v>
       </c>
       <c r="K46" s="5">
-        <v>9102126441</v>
-      </c>
-      <c r="L46" s="5">
         <v>471086727801</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O46" s="2" t="s">
+      <c r="L46" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N46" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>35</v>
+      <c r="O46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q46" s="5">
         <v>12</v>
@@ -5050,50 +5048,50 @@
       <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="B47" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="C47" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="F47" s="2" t="s">
+      <c r="D47" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="F47" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G47" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>24</v>
+      <c r="G47" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="5">
+        <v>39307</v>
       </c>
       <c r="J47" s="5">
-        <v>39307</v>
+        <v>9199581775</v>
       </c>
       <c r="K47" s="5">
-        <v>9199581775</v>
-      </c>
-      <c r="L47" s="5">
         <v>901768624746</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O47" s="2" t="s">
+      <c r="L47" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N47" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P47" s="2" t="s">
-        <v>35</v>
+      <c r="O47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q47" s="5">
         <v>12</v>
@@ -5103,48 +5101,48 @@
       <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="D48" s="2" t="s">
+      <c r="B48" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="C48" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="D48" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G48" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>59</v>
+      <c r="G48" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" s="5">
+        <v>38718</v>
       </c>
       <c r="J48" s="5">
-        <v>38718</v>
-      </c>
-      <c r="K48" s="5">
         <v>6203624935</v>
       </c>
-      <c r="L48" s="5"/>
-      <c r="M48" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O48" s="2" t="s">
+      <c r="K48" s="5"/>
+      <c r="L48" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P48" s="2" t="s">
-        <v>35</v>
+      <c r="O48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q48" s="5">
         <v>12</v>
@@ -5154,50 +5152,50 @@
       <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="B49" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="C49" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="D49" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="F49" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>24</v>
+      <c r="G49" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="5">
+        <v>39344</v>
       </c>
       <c r="J49" s="5">
-        <v>39344</v>
+        <v>7488797688</v>
       </c>
       <c r="K49" s="5">
-        <v>7488797688</v>
-      </c>
-      <c r="L49" s="5">
         <v>838349076791</v>
       </c>
-      <c r="M49" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O49" s="2" t="s">
+      <c r="L49" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N49" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P49" s="2" t="s">
-        <v>35</v>
+      <c r="O49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q49" s="5">
         <v>12</v>
@@ -5207,50 +5205,50 @@
       <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D50" s="2" t="s">
+      <c r="B50" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="C50" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="D50" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F50" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>24</v>
+      <c r="G50" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="5">
+        <v>37079</v>
       </c>
       <c r="J50" s="5">
-        <v>37079</v>
+        <v>7903378879</v>
       </c>
       <c r="K50" s="5">
-        <v>7903378879</v>
-      </c>
-      <c r="L50" s="5">
         <v>393619738142</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="N50" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O50" s="2" t="s">
+      <c r="L50" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>35</v>
+      <c r="O50" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q50" s="5">
         <v>12</v>
@@ -5260,50 +5258,50 @@
       <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="B51" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="C51" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="D51" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>24</v>
+      <c r="G51" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="5">
+        <v>38181</v>
       </c>
       <c r="J51" s="5">
-        <v>38181</v>
+        <v>7782920026</v>
       </c>
       <c r="K51" s="5">
-        <v>7782920026</v>
-      </c>
-      <c r="L51" s="5">
         <v>916139525681</v>
       </c>
-      <c r="M51" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O51" s="2" t="s">
+      <c r="L51" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N51" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P51" s="2" t="s">
-        <v>35</v>
+      <c r="O51" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q51" s="5">
         <v>12</v>
@@ -5313,50 +5311,50 @@
       <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="B52" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="C52" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="D52" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>86</v>
+      <c r="G52" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I52" s="5">
+        <v>38865</v>
       </c>
       <c r="J52" s="5">
-        <v>38865</v>
+        <v>9470647079</v>
       </c>
       <c r="K52" s="5">
-        <v>9470647079</v>
-      </c>
-      <c r="L52" s="5">
         <v>940669655059</v>
       </c>
-      <c r="M52" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O52" s="2" t="s">
+      <c r="L52" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P52" s="2" t="s">
-        <v>35</v>
+      <c r="O52" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q52" s="5">
         <v>12</v>
@@ -5366,50 +5364,50 @@
       <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="B53" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="C53" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="D53" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="F53" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G53" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>86</v>
+      <c r="G53" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I53" s="5">
+        <v>38883</v>
       </c>
       <c r="J53" s="5">
-        <v>38883</v>
+        <v>7361833938</v>
       </c>
       <c r="K53" s="5">
-        <v>7361833938</v>
-      </c>
-      <c r="L53" s="5">
         <v>687604314121</v>
       </c>
-      <c r="M53" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O53" s="2" t="s">
+      <c r="L53" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N53" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P53" s="2" t="s">
-        <v>35</v>
+      <c r="O53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q53" s="5">
         <v>12</v>
@@ -5419,50 +5417,50 @@
       <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="B54" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="C54" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="D54" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F54" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>24</v>
+      <c r="G54" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="5">
+        <v>39518</v>
       </c>
       <c r="J54" s="5">
-        <v>39518</v>
+        <v>7061686327</v>
       </c>
       <c r="K54" s="5">
-        <v>7061686327</v>
-      </c>
-      <c r="L54" s="5">
         <v>856757355690</v>
       </c>
-      <c r="M54" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="N54" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P54" s="2" t="s">
-        <v>35</v>
+      <c r="L54" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N54" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q54" s="5">
         <v>12</v>
@@ -5472,50 +5470,50 @@
       <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="B55" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="C55" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="D55" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F55" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="4" t="s">
+      <c r="G55" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="2" t="s">
-        <v>24</v>
+      <c r="I55" s="5">
+        <v>39443</v>
       </c>
       <c r="J55" s="5">
-        <v>39443</v>
+        <v>9142073003</v>
       </c>
       <c r="K55" s="5">
-        <v>9142073003</v>
-      </c>
-      <c r="L55" s="5">
         <v>630314063489</v>
       </c>
-      <c r="M55" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>35</v>
+      <c r="L55" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q55" s="5">
         <v>12</v>
@@ -5525,50 +5523,50 @@
       <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="B56" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="C56" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="D56" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="F56" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="4" t="s">
+      <c r="G56" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H56" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>86</v>
+      <c r="H56" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I56" s="5">
+        <v>38906</v>
       </c>
       <c r="J56" s="5">
-        <v>38906</v>
+        <v>8877573957</v>
       </c>
       <c r="K56" s="5">
-        <v>8877573957</v>
-      </c>
-      <c r="L56" s="5">
         <v>668133220409</v>
       </c>
-      <c r="M56" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P56" s="2" t="s">
-        <v>35</v>
+      <c r="L56" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q56" s="5">
         <v>12</v>
@@ -5578,50 +5576,50 @@
       <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="B57" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="F57" s="2" t="s">
+      <c r="C57" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F57" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G57" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>24</v>
+      <c r="G57" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="5">
+        <v>39083</v>
       </c>
       <c r="J57" s="5">
-        <v>39083</v>
+        <v>7050791121</v>
       </c>
       <c r="K57" s="5">
-        <v>7050791121</v>
-      </c>
-      <c r="L57" s="5">
         <v>998616762700</v>
       </c>
-      <c r="M57" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O57" s="2" t="s">
+      <c r="L57" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P57" s="2" t="s">
-        <v>35</v>
+      <c r="O57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q57" s="5">
         <v>12</v>
@@ -5631,50 +5629,50 @@
       <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="B58" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="C58" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="D58" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="F58" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>24</v>
+      <c r="G58" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="5">
+        <v>38981</v>
       </c>
       <c r="J58" s="5">
-        <v>38981</v>
+        <v>7909096009</v>
       </c>
       <c r="K58" s="5">
-        <v>7909096009</v>
-      </c>
-      <c r="L58" s="5">
         <v>517760953983</v>
       </c>
-      <c r="M58" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="N58" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O58" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>35</v>
+      <c r="L58" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q58" s="5">
         <v>12</v>
@@ -5684,50 +5682,50 @@
       <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F59" s="2" t="s">
+      <c r="B59" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="F59" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G59" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>24</v>
+      <c r="G59" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="5">
+        <v>38409</v>
       </c>
       <c r="J59" s="5">
-        <v>38409</v>
+        <v>6207838600</v>
       </c>
       <c r="K59" s="5">
-        <v>6207838600</v>
-      </c>
-      <c r="L59" s="5">
         <v>814205502465</v>
       </c>
-      <c r="M59" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="N59" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>35</v>
+      <c r="L59" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N59" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q59" s="5">
         <v>12</v>
@@ -5737,50 +5735,50 @@
       <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="B60" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="C60" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="D60" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F60" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>24</v>
+      <c r="G60" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="5">
+        <v>38722</v>
       </c>
       <c r="J60" s="5">
-        <v>38722</v>
+        <v>7543042872</v>
       </c>
       <c r="K60" s="5">
-        <v>7543042872</v>
-      </c>
-      <c r="L60" s="5">
         <v>856730494677</v>
       </c>
-      <c r="M60" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O60" s="2" t="s">
+      <c r="L60" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N60" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="P60" s="2" t="s">
-        <v>35</v>
+      <c r="O60" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q60" s="5">
         <v>12</v>
@@ -5790,103 +5788,103 @@
       <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="B61" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="C61" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="D61" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F61" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G61" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>24</v>
+      <c r="G61" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="5">
+        <v>38655</v>
       </c>
       <c r="J61" s="5">
-        <v>38655</v>
+        <v>7070025124</v>
       </c>
       <c r="K61" s="5">
-        <v>7070025124</v>
-      </c>
-      <c r="L61" s="5">
         <v>589737972896</v>
       </c>
-      <c r="M61" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>35</v>
+      <c r="L61" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N61" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="Q61" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="62" customHeight="1" spans="1:17">
-      <c r="A62" s="3">
+      <c r="A62" s="4">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="B62" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="C62" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="D62" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="G62" s="4" t="s">
+      <c r="E62" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H62" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="I62" s="4">
         <v>39448</v>
       </c>
-      <c r="K62" s="3">
+      <c r="J62" s="4">
         <v>9155258427</v>
       </c>
-      <c r="L62" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="N62" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O62" s="4" t="s">
+      <c r="K62" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="P62" s="2" t="s">
+      <c r="L62" s="3" t="s">
         <v>324</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>326</v>
       </c>
       <c r="Q62" s="5">
         <v>13</v>
@@ -5896,48 +5894,48 @@
       <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B63" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I63" s="5">
+        <v>38295</v>
+      </c>
+      <c r="J63" s="5">
+        <v>9006996045</v>
+      </c>
+      <c r="K63" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="L63" s="5"/>
+      <c r="M63" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N63" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J63" s="5">
-        <v>38295</v>
-      </c>
-      <c r="K63" s="5">
-        <v>9006996045</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="M63" s="5"/>
-      <c r="N63" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O63" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P63" s="2" t="s">
-        <v>331</v>
+      <c r="O63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q63" s="5">
         <v>13</v>
@@ -5947,50 +5945,50 @@
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="B64" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I64" s="5">
+        <v>39178</v>
+      </c>
+      <c r="J64" s="5">
+        <v>9162021714</v>
+      </c>
+      <c r="K64" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N64" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P64" s="6" t="s">
         <v>333</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J64" s="5">
-        <v>39178</v>
-      </c>
-      <c r="K64" s="5">
-        <v>9162021714</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O64" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="P64" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="Q64" s="5">
         <v>13</v>
@@ -6000,50 +5998,50 @@
       <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="B65" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="C65" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G65" s="4" t="s">
+      <c r="D65" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G65" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H65" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>59</v>
+      <c r="H65" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I65" s="5">
+        <v>39373</v>
       </c>
       <c r="J65" s="5">
-        <v>39373</v>
-      </c>
-      <c r="K65" s="5">
         <v>8757013088</v>
       </c>
-      <c r="L65" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O65" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>331</v>
+      <c r="K65" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q65" s="5">
         <v>13</v>
@@ -6053,48 +6051,48 @@
       <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D66" s="2" t="s">
+      <c r="B66" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="E66" s="2" t="s">
+      <c r="C66" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G66" s="4" t="s">
+      <c r="D66" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G66" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H66" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>180</v>
+      <c r="H66" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I66" s="5">
+        <v>38430</v>
       </c>
       <c r="J66" s="5">
-        <v>38430</v>
-      </c>
-      <c r="K66" s="5">
         <v>9006986035</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M66" s="5"/>
-      <c r="N66" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P66" s="2" t="s">
-        <v>331</v>
+      <c r="K66" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="L66" s="5"/>
+      <c r="M66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N66" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q66" s="5">
         <v>13</v>
@@ -6104,50 +6102,50 @@
       <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="D67" s="2" t="s">
+      <c r="B67" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G67" s="4" t="s">
+      <c r="C67" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G67" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H67" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>329</v>
+      <c r="H67" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I67" s="5">
+        <v>38975</v>
       </c>
       <c r="J67" s="5">
-        <v>38975</v>
-      </c>
-      <c r="K67" s="5">
         <v>7543020820</v>
       </c>
-      <c r="L67" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="M67" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="N67" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O67" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P67" s="2" t="s">
-        <v>331</v>
+      <c r="K67" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N67" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q67" s="5">
         <v>13</v>
@@ -6157,50 +6155,50 @@
       <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D68" s="2" t="s">
+      <c r="B68" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="E68" s="2" t="s">
+      <c r="C68" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G68" s="4" t="s">
+      <c r="D68" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>329</v>
+      <c r="H68" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I68" s="5">
+        <v>39347</v>
       </c>
       <c r="J68" s="5">
-        <v>39347</v>
-      </c>
-      <c r="K68" s="5">
         <v>9122623897</v>
       </c>
-      <c r="L68" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O68" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>331</v>
+      <c r="K68" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N68" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q68" s="5">
         <v>13</v>
@@ -6210,48 +6208,48 @@
       <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D69" s="2" t="s">
+      <c r="B69" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="E69" s="2" t="s">
+      <c r="C69" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G69" s="4" t="s">
+      <c r="D69" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G69" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H69" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>59</v>
+      <c r="H69" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I69" s="5">
+        <v>38969</v>
       </c>
       <c r="J69" s="5">
-        <v>38969</v>
-      </c>
-      <c r="K69" s="5">
         <v>8102890014</v>
       </c>
-      <c r="L69" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="M69" s="5"/>
-      <c r="N69" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O69" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P69" s="2" t="s">
-        <v>331</v>
+      <c r="K69" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="L69" s="5"/>
+      <c r="M69" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N69" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q69" s="5">
         <v>13</v>
@@ -6261,50 +6259,50 @@
       <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="D70" s="2" t="s">
+      <c r="B70" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="E70" s="2" t="s">
+      <c r="C70" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G70" s="4" t="s">
+      <c r="D70" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H70" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>329</v>
+      <c r="H70" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I70" s="5">
+        <v>38542</v>
       </c>
       <c r="J70" s="5">
-        <v>38542</v>
-      </c>
-      <c r="K70" s="5">
         <v>9471956435</v>
       </c>
-      <c r="L70" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="M70" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="O70" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="P70" s="2" t="s">
-        <v>331</v>
+      <c r="K70" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="N70" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q70" s="5">
         <v>13</v>
@@ -6314,50 +6312,50 @@
       <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D71" s="2" t="s">
+      <c r="B71" s="6" t="s">
         <v>374</v>
       </c>
-      <c r="E71" s="2" t="s">
+      <c r="C71" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G71" s="4" t="s">
+      <c r="D71" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G71" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H71" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>59</v>
+      <c r="H71" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I71" s="5">
+        <v>34750</v>
       </c>
       <c r="J71" s="5">
-        <v>34750</v>
-      </c>
-      <c r="K71" s="5">
         <v>9430282519</v>
       </c>
-      <c r="L71" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="M71" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="N71" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O71" s="2" t="s">
+      <c r="K71" s="6" t="s">
         <v>378</v>
       </c>
-      <c r="P71" s="2" t="s">
-        <v>331</v>
+      <c r="L71" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N71" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="O71" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q71" s="5">
         <v>13</v>
@@ -6367,50 +6365,50 @@
       <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D72" s="2" t="s">
+      <c r="B72" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="C72" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G72" s="4" t="s">
+      <c r="D72" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G72" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>59</v>
+      <c r="H72" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I72" s="5">
+        <v>39480</v>
       </c>
       <c r="J72" s="5">
-        <v>39480</v>
-      </c>
-      <c r="K72" s="5">
         <v>7979711275</v>
       </c>
-      <c r="L72" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="N72" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O72" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P72" s="2" t="s">
-        <v>331</v>
+      <c r="K72" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N72" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O72" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q72" s="5">
         <v>13</v>
@@ -6420,50 +6418,50 @@
       <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G73" s="4" t="s">
+      <c r="B73" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G73" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H73" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>59</v>
+      <c r="H73" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I73" s="5">
+        <v>39264</v>
       </c>
       <c r="J73" s="5">
-        <v>39264</v>
-      </c>
-      <c r="K73" s="5">
         <v>7488468875</v>
       </c>
-      <c r="L73" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="N73" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O73" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P73" s="2" t="s">
-        <v>331</v>
+      <c r="K73" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N73" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O73" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q73" s="5">
         <v>13</v>
@@ -6473,48 +6471,48 @@
       <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D74" s="2" t="s">
+      <c r="B74" s="6" t="s">
         <v>391</v>
       </c>
-      <c r="E74" s="2" t="s">
+      <c r="C74" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G74" s="4" t="s">
+      <c r="D74" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H74" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>329</v>
+      <c r="H74" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I74" s="5">
+        <v>38805</v>
       </c>
       <c r="J74" s="5">
-        <v>38805</v>
-      </c>
-      <c r="K74" s="5">
         <v>8877916097</v>
       </c>
-      <c r="L74" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="M74" s="5"/>
-      <c r="N74" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P74" s="2" t="s">
-        <v>331</v>
+      <c r="K74" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="L74" s="5"/>
+      <c r="M74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O74" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q74" s="5">
         <v>13</v>
@@ -6524,50 +6522,50 @@
       <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G75" s="4" t="s">
+      <c r="B75" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G75" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H75" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75" s="2" t="s">
-        <v>59</v>
+      <c r="H75" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I75" s="5">
+        <v>39128</v>
       </c>
       <c r="J75" s="5">
-        <v>39128</v>
-      </c>
-      <c r="K75" s="5">
         <v>7765003737</v>
       </c>
-      <c r="L75" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="M75" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="N75" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O75" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P75" s="2" t="s">
-        <v>331</v>
+      <c r="K75" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N75" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O75" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q75" s="5">
         <v>13</v>
@@ -6577,50 +6575,50 @@
       <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="D76" s="2" t="s">
+      <c r="B76" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="E76" s="2" t="s">
+      <c r="C76" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G76" s="4" t="s">
+      <c r="D76" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G76" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H76" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>401</v>
+      <c r="H76" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I76" s="5">
+        <v>38775</v>
       </c>
       <c r="J76" s="5">
-        <v>38775</v>
-      </c>
-      <c r="K76" s="5">
         <v>8084266154</v>
       </c>
-      <c r="L76" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="M76" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="N76" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O76" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P76" s="2" t="s">
-        <v>331</v>
+      <c r="K76" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N76" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O76" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q76" s="5">
         <v>13</v>
@@ -6630,101 +6628,101 @@
       <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="D77" s="2" t="s">
+      <c r="B77" s="6" t="s">
         <v>406</v>
       </c>
-      <c r="E77" s="2" t="s">
+      <c r="C77" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G77" s="4" t="s">
+      <c r="D77" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G77" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H77" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>59</v>
+      <c r="H77" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I77" s="5">
+        <v>38718</v>
       </c>
       <c r="J77" s="5">
-        <v>38718</v>
-      </c>
-      <c r="K77" s="5">
         <v>9570065414</v>
       </c>
-      <c r="L77" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="M77" s="5"/>
-      <c r="N77" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O77" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="P77" s="2" t="s">
-        <v>331</v>
+      <c r="K77" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="L77" s="5"/>
+      <c r="M77" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N77" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>333</v>
       </c>
       <c r="Q77" s="5">
         <v>13</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="1:17">
-      <c r="A78" s="3">
+      <c r="A78" s="4">
         <v>77</v>
       </c>
-      <c r="B78" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="D78" s="4" t="s">
+      <c r="B78" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="C78" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="J78" s="4" t="s">
+      <c r="D78" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="K78" s="3">
+      <c r="E78" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="J78" s="4">
         <v>9031870915</v>
       </c>
-      <c r="L78" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="M78" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="N78" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O78" s="4" t="s">
+      <c r="K78" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="P78" s="2" t="s">
+      <c r="L78" s="3" t="s">
         <v>417</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N78" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="O78" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>419</v>
       </c>
       <c r="Q78" s="5">
         <v>16</v>
@@ -6734,50 +6732,50 @@
       <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="B79" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I79" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="J79" s="5">
+        <v>9341855985</v>
+      </c>
+      <c r="K79" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N79" s="6" t="s">
         <v>418</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="K79" s="5">
-        <v>9341855985</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="M79" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="N79" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="P79" s="2" t="s">
-        <v>425</v>
+      <c r="O79" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="Q79" s="5">
         <v>16</v>
@@ -6787,50 +6785,50 @@
       <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C80" s="2" t="s">
+      <c r="B80" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I80" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="J80" s="5">
+        <v>9693407905</v>
+      </c>
+      <c r="K80" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="O80" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P80" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="K80" s="5">
-        <v>9693407905</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="M80" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O80" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="Q80" s="5">
         <v>16</v>
@@ -6840,50 +6838,50 @@
       <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="D81" s="2" t="s">
+      <c r="B81" s="6" t="s">
         <v>435</v>
       </c>
-      <c r="E81" s="2" t="s">
+      <c r="C81" s="6" t="s">
         <v>436</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I81" s="2" t="s">
+      <c r="D81" s="6" t="s">
         <v>437</v>
       </c>
-      <c r="J81" s="2" t="s">
+      <c r="E81" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="K81" s="5">
+      <c r="F81" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="I81" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="J81" s="5">
         <v>9113433726</v>
       </c>
-      <c r="L81" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="M81" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="N81" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O81" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P81" s="2" t="s">
-        <v>425</v>
+      <c r="K81" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O81" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="Q81" s="5">
         <v>16</v>
@@ -6893,48 +6891,48 @@
       <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D82" s="2" t="s">
+      <c r="B82" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="E82" s="2" t="s">
+      <c r="C82" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G82" s="4" t="s">
+      <c r="D82" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G82" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H82" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="K82" s="5">
+      <c r="H82" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I82" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="J82" s="5">
         <v>9241726202</v>
       </c>
-      <c r="L82" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="M82" s="5"/>
-      <c r="N82" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="P82" s="2" t="s">
-        <v>425</v>
+      <c r="K82" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="L82" s="5"/>
+      <c r="M82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N82" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="O82" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="Q82" s="5">
         <v>16</v>
@@ -6944,48 +6942,48 @@
       <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="D83" s="2" t="s">
+      <c r="B83" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="E83" s="2" t="s">
+      <c r="C83" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J83" s="2" t="s">
+      <c r="D83" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="K83" s="5">
+      <c r="E83" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I83" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="J83" s="5">
         <v>9341829406</v>
       </c>
-      <c r="L83" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="M83" s="5"/>
-      <c r="N83" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O83" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="P83" s="2" t="s">
-        <v>425</v>
+      <c r="K83" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="L83" s="5"/>
+      <c r="M83" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="Q83" s="5">
         <v>16</v>
@@ -6995,50 +6993,50 @@
       <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D84" s="2" t="s">
+      <c r="B84" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="E84" s="2" t="s">
+      <c r="C84" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I84" s="2" t="s">
+      <c r="D84" s="6" t="s">
         <v>457</v>
       </c>
-      <c r="J84" s="2" t="s">
+      <c r="E84" s="6" t="s">
         <v>458</v>
       </c>
-      <c r="K84" s="5">
+      <c r="F84" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="I84" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="J84" s="5">
         <v>8927434942</v>
       </c>
-      <c r="L84" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="M84" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="N84" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" s="2" t="s">
+      <c r="K84" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="P84" s="2" t="s">
-        <v>425</v>
+      <c r="L84" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="Q84" s="5">
         <v>16</v>
@@ -7048,103 +7046,103 @@
       <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D85" s="2" t="s">
+      <c r="B85" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="E85" s="2" t="s">
+      <c r="C85" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G85" s="4" t="s">
+      <c r="D85" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G85" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H85" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="K85" s="5">
+      <c r="H85" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="I85" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="J85" s="5">
         <v>9334621848</v>
       </c>
-      <c r="L85" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="M85" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="N85" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O85" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="P85" s="2" t="s">
-        <v>425</v>
+      <c r="K85" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N85" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="O85" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>427</v>
       </c>
       <c r="Q85" s="5">
         <v>16</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="1:17">
-      <c r="A86" s="3">
+      <c r="A86" s="4">
         <v>85</v>
       </c>
-      <c r="B86" s="4" t="s">
-        <v>469</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="D86" s="4" t="s">
+      <c r="B86" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="E86" s="4" t="s">
+      <c r="C86" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="J86" s="4" t="s">
+      <c r="D86" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="K86" s="3">
+      <c r="E86" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="J86" s="4">
         <v>9664020656</v>
       </c>
-      <c r="L86" s="3">
+      <c r="K86" s="4">
         <v>351271180893</v>
       </c>
-      <c r="M86" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="N86" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="O86" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="P86" s="2" t="s">
+      <c r="L86" s="3" t="s">
         <v>476</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N86" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="O86" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>478</v>
       </c>
       <c r="Q86" s="5">
         <v>35</v>
@@ -7154,50 +7152,50 @@
       <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D87" s="2" t="s">
+      <c r="B87" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="E87" s="2" t="s">
+      <c r="C87" s="6" t="s">
         <v>480</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="G87" s="4" t="s">
+      <c r="D87" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="G87" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="H87" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>481</v>
+      <c r="H87" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I87" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="J87" s="5">
+        <v>6205404849</v>
       </c>
       <c r="K87" s="5">
-        <v>6205404849</v>
-      </c>
-      <c r="L87" s="5">
         <v>789286512022</v>
       </c>
-      <c r="M87" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="N87" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O87" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="P87" s="2" t="s">
+      <c r="L87" s="6" t="s">
         <v>484</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N87" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="O87" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>486</v>
       </c>
       <c r="Q87" s="5">
         <v>35</v>
@@ -7205,24 +7203,24 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="M61" r:id="rId1" display="pandeyaditya59829@gmail.com"/>
-    <hyperlink ref="M62" r:id="rId2" display="komalkumari54343489000@gmail.com"/>
-    <hyperlink ref="M64" r:id="rId3" display="dutta2052@gmail.com"/>
-    <hyperlink ref="M65" r:id="rId4" display="guriyakumariktr371@gmail.com"/>
-    <hyperlink ref="M67" r:id="rId5" display="sj099048@gmail.com"/>
-    <hyperlink ref="M68" r:id="rId6" display="khushi22sinha@gmail.com"/>
-    <hyperlink ref="M70" r:id="rId7" display="srishtishrivastava3009@gmail.com"/>
-    <hyperlink ref="M71" r:id="rId8" display="shahestanaaznaaz@mail.com"/>
-    <hyperlink ref="M73" r:id="rId9" display="sakshirinky5@gmail.com"/>
-    <hyperlink ref="M76" r:id="rId10" display="mishrariddhi658@gmail.com"/>
-    <hyperlink ref="M78" r:id="rId11" display="kw317347@gmail.com"/>
-    <hyperlink ref="M79" r:id="rId12" display="arajahan931@gmail.com"/>
-    <hyperlink ref="M80" r:id="rId13" display="unstablezeya@gmail.com"/>
-    <hyperlink ref="M81" r:id="rId14" display="Daksh3409@gmail.com"/>
-    <hyperlink ref="M84" r:id="rId15" display="itziftikar@gmail.com"/>
-    <hyperlink ref="M85" r:id="rId16" display="goutamipaul5@gmail.com"/>
-    <hyperlink ref="M86" r:id="rId17" display="hamidiqubal123@gmail.com"/>
-    <hyperlink ref="M87" r:id="rId18" display="yogitathakurchanchal@gmail.com"/>
+    <hyperlink ref="L61" r:id="rId1" display="pandeyaditya59829@gmail.com" tooltip="mailto:pandeyaditya59829@gmail.com"/>
+    <hyperlink ref="L62" r:id="rId2" display="komalkumari54343489000@gmail.com" tooltip="mailto:komalkumari54343489000@gmail.com"/>
+    <hyperlink ref="L64" r:id="rId3" display="dutta2052@gmail.com" tooltip="mailto:dutta2052@gmail.com"/>
+    <hyperlink ref="L65" r:id="rId4" display="guriyakumariktr371@gmail.com" tooltip="mailto:guriyakumariktr371@gmail.com"/>
+    <hyperlink ref="L67" r:id="rId5" display="sj099048@gmail.com" tooltip="mailto:sj099048@gmail.com"/>
+    <hyperlink ref="L68" r:id="rId6" display="khushi22sinha@gmail.com" tooltip="mailto:khushi22sinha@gmail.com"/>
+    <hyperlink ref="L70" r:id="rId7" display="srishtishrivastava3009@gmail.com" tooltip="mailto:srishtishrivastava3009@gmail.com"/>
+    <hyperlink ref="L71" r:id="rId8" display="shahestanaaznaaz@mail.com" tooltip="mailto:shahestanaaznaaz@mail.com"/>
+    <hyperlink ref="L73" r:id="rId9" display="sakshirinky5@gmail.com" tooltip="mailto:sakshirinky5@gmail.com"/>
+    <hyperlink ref="L76" r:id="rId10" display="mishrariddhi658@gmail.com" tooltip="mailto:mishrariddhi658@gmail.com"/>
+    <hyperlink ref="L78" r:id="rId11" display="kw317347@gmail.com" tooltip="mailto:kw317347@gmail.com"/>
+    <hyperlink ref="L79" r:id="rId12" display="arajahan931@gmail.com" tooltip="mailto:arajahan931@gmail.com"/>
+    <hyperlink ref="L80" r:id="rId13" display="unstablezeya@gmail.com" tooltip="mailto:unstablezeya@gmail.com"/>
+    <hyperlink ref="L81" r:id="rId14" display="Daksh3409@gmail.com" tooltip="mailto:Daksh3409@gmail.com"/>
+    <hyperlink ref="L84" r:id="rId15" display="itziftikar@gmail.com" tooltip="mailto:itziftikar@gmail.com"/>
+    <hyperlink ref="L85" r:id="rId16" display="goutamipaul5@gmail.com" tooltip="mailto:goutamipaul5@gmail.com"/>
+    <hyperlink ref="L86" r:id="rId17" display="hamidiqubal123@gmail.com" tooltip="mailto:hamidiqubal123@gmail.com"/>
+    <hyperlink ref="L87" r:id="rId18" display="yogitathakurchanchal@gmail.com" tooltip="mailto:yogitathakurchanchal@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.196850393700787" right="0.196850393700787" top="0.196850393700787" bottom="0.196850393700787" header="0" footer="0"/>
   <pageSetup paperSize="5" scale="79" orientation="landscape"/>
